--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.36848637730223</v>
+        <v>12.24737903631161</v>
       </c>
       <c r="D2" t="n">
-        <v>47.12459696595642</v>
+        <v>7.657747006967918</v>
       </c>
       <c r="E2" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F2" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>77.33193657194796</v>
+        <v>12.56643969294154</v>
       </c>
       <c r="D3" t="n">
-        <v>5.903787255346177</v>
+        <v>0.9593654289937538</v>
       </c>
       <c r="E3" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F3" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>90.68372306942994</v>
+        <v>14.73610499878237</v>
       </c>
       <c r="D4" t="n">
-        <v>63.28222993068433</v>
+        <v>10.2833623637362</v>
       </c>
       <c r="E4" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F4" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>67.09087029546254</v>
+        <v>10.90226642301266</v>
       </c>
       <c r="D5" t="n">
-        <v>34.53129274855444</v>
+        <v>5.611335071640097</v>
       </c>
       <c r="E5" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F5" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.91451636269856</v>
+        <v>10.22360890893852</v>
       </c>
       <c r="D6" t="n">
-        <v>22.23907303289774</v>
+        <v>3.613849367845883</v>
       </c>
       <c r="E6" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F6" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>82.70218933749373</v>
+        <v>13.43910576734273</v>
       </c>
       <c r="D7" t="n">
-        <v>51.79285665031424</v>
+        <v>8.416339205676065</v>
       </c>
       <c r="E7" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F7" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>78.47268288772915</v>
+        <v>12.75181096925599</v>
       </c>
       <c r="D8" t="n">
-        <v>43.15669125408017</v>
+        <v>7.012962328788028</v>
       </c>
       <c r="E8" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F8" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>82.07162052964928</v>
+        <v>13.33663833606801</v>
       </c>
       <c r="D9" t="n">
-        <v>22.74313083108832</v>
+        <v>3.695758760051852</v>
       </c>
       <c r="E9" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F9" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>55.86265691164053</v>
+        <v>9.077681748141588</v>
       </c>
       <c r="D10" t="n">
-        <v>8.152651988275053</v>
+        <v>1.324805948094696</v>
       </c>
       <c r="E10" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F10" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.30424758958456</v>
+        <v>8.82444023330749</v>
       </c>
       <c r="D11" t="n">
-        <v>4.749167916169269</v>
+        <v>0.7717397863775063</v>
       </c>
       <c r="E11" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F11" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>76.07435199106052</v>
+        <v>12.36208219854734</v>
       </c>
       <c r="D12" t="n">
-        <v>41.30980513146969</v>
+        <v>6.712843333863826</v>
       </c>
       <c r="E12" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F12" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.66323419930035</v>
+        <v>8.720275557386309</v>
       </c>
       <c r="D13" t="n">
-        <v>14.30667068147531</v>
+        <v>2.324833985739739</v>
       </c>
       <c r="E13" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F13" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.07327899127591</v>
+        <v>10.24940783608234</v>
       </c>
       <c r="D14" t="n">
-        <v>29.5106892794667</v>
+        <v>4.795487007913338</v>
       </c>
       <c r="E14" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F14" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>45.28960554141164</v>
+        <v>7.359560900479392</v>
       </c>
       <c r="D15" t="n">
-        <v>7.547301914456345</v>
+        <v>1.226436561099156</v>
       </c>
       <c r="E15" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F15" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>74.79168338027624</v>
+        <v>12.15364854929489</v>
       </c>
       <c r="D16" t="n">
-        <v>29.90819285747636</v>
+        <v>4.860081339339909</v>
       </c>
       <c r="E16" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F16" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>50.25412904672324</v>
+        <v>8.166295970092525</v>
       </c>
       <c r="D17" t="n">
-        <v>25.25989863851132</v>
+        <v>4.104733528758089</v>
       </c>
       <c r="E17" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F17" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>45.87197529505411</v>
+        <v>7.454195985446294</v>
       </c>
       <c r="D18" t="n">
-        <v>26.76751762864835</v>
+        <v>4.349721614655357</v>
       </c>
       <c r="E18" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F18" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>66.46958418907178</v>
+        <v>10.80130743072417</v>
       </c>
       <c r="D19" t="n">
-        <v>39.88877330600026</v>
+        <v>6.481925662225042</v>
       </c>
       <c r="E19" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F19" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>54.54684002069418</v>
+        <v>8.863861503362806</v>
       </c>
       <c r="D20" t="n">
-        <v>25.07288794923484</v>
+        <v>4.074344291750661</v>
       </c>
       <c r="E20" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F20" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>53.03930400151797</v>
+        <v>8.61888690024667</v>
       </c>
       <c r="D21" t="n">
-        <v>20.0585687872829</v>
+        <v>3.259517427933472</v>
       </c>
       <c r="E21" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F21" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>60.20913517936626</v>
+        <v>9.783984466647018</v>
       </c>
       <c r="D22" t="n">
-        <v>23.3238075793812</v>
+        <v>3.790118731649446</v>
       </c>
       <c r="E22" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F22" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>40.05196413119337</v>
+        <v>6.508444171318922</v>
       </c>
       <c r="D23" t="n">
-        <v>4.716990566028302</v>
+        <v>0.7665109669795991</v>
       </c>
       <c r="E23" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F23" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>63.38929387609625</v>
+        <v>10.30076025486564</v>
       </c>
       <c r="D24" t="n">
-        <v>46.62023965577751</v>
+        <v>7.575788944063846</v>
       </c>
       <c r="E24" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F24" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>45.84104782853906</v>
+        <v>7.449170272137597</v>
       </c>
       <c r="D25" t="n">
-        <v>15.96572331551733</v>
+        <v>2.594430038771566</v>
       </c>
       <c r="E25" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F25" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>49.67034259478072</v>
+        <v>8.071430671651868</v>
       </c>
       <c r="D26" t="n">
-        <v>12.7264885308727</v>
+        <v>2.068054386266814</v>
       </c>
       <c r="E26" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F26" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>38.9179592844736</v>
+        <v>6.324168383726961</v>
       </c>
       <c r="D27" t="n">
-        <v>7.007103979022961</v>
+        <v>1.138654396591231</v>
       </c>
       <c r="E27" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F27" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>25.30399273663365</v>
+        <v>4.111898819702968</v>
       </c>
       <c r="D28" t="n">
-        <v>15.56853074377574</v>
+        <v>2.529886245863559</v>
       </c>
       <c r="E28" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F28" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>21.5621362184797</v>
+        <v>3.503847135502951</v>
       </c>
       <c r="D29" t="n">
-        <v>24.2010419981215</v>
+        <v>3.932669324694743</v>
       </c>
       <c r="E29" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F29" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>30.34998910049701</v>
+        <v>4.931873228830765</v>
       </c>
       <c r="D30" t="n">
-        <v>11.5974135047432</v>
+        <v>1.88457969452077</v>
       </c>
       <c r="E30" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F30" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>36.26717716071024</v>
+        <v>5.893416288615414</v>
       </c>
       <c r="D31" t="n">
-        <v>22.41007837233777</v>
+        <v>3.641637735504887</v>
       </c>
       <c r="E31" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F31" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>20.170445236199</v>
+        <v>3.277697350882338</v>
       </c>
       <c r="D32" t="n">
-        <v>20.30394050424695</v>
+        <v>3.29939033194013</v>
       </c>
       <c r="E32" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F32" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>39.0345774677913</v>
+        <v>6.343118838516086</v>
       </c>
       <c r="D33" t="n">
-        <v>31.00101734164079</v>
+        <v>5.037665318016628</v>
       </c>
       <c r="E33" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F33" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>35.23256923035188</v>
+        <v>5.725292499932181</v>
       </c>
       <c r="D34" t="n">
-        <v>7.516648189186454</v>
+        <v>1.221455330742799</v>
       </c>
       <c r="E34" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F34" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>25.32316958378464</v>
+        <v>4.115015057365004</v>
       </c>
       <c r="D35" t="n">
-        <v>24.66055883232943</v>
+        <v>4.007340810253532</v>
       </c>
       <c r="E35" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F35" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>28.51952902071065</v>
+        <v>4.63442346586548</v>
       </c>
       <c r="D36" t="n">
-        <v>10.96585609973065</v>
+        <v>1.781951616206231</v>
       </c>
       <c r="E36" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F36" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>63.84740725375971</v>
+        <v>10.37520367873595</v>
       </c>
       <c r="D37" t="n">
-        <v>35.35533905932738</v>
+        <v>5.745242597140699</v>
       </c>
       <c r="E37" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F37" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>10.74700701113844</v>
+        <v>1.746388639309997</v>
       </c>
       <c r="D38" t="n">
-        <v>9.108015217549829</v>
+        <v>1.480052472851847</v>
       </c>
       <c r="E38" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F38" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>32.47441372647094</v>
+        <v>5.277092230551527</v>
       </c>
       <c r="D39" t="n">
-        <v>30.51953462047546</v>
+        <v>4.959424375827262</v>
       </c>
       <c r="E39" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F39" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>17.43555463972417</v>
+        <v>2.833277628955178</v>
       </c>
       <c r="D40" t="n">
-        <v>17.60830810151628</v>
+        <v>2.861350066496395</v>
       </c>
       <c r="E40" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F40" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>16.19052302260922</v>
+        <v>2.630959991173998</v>
       </c>
       <c r="D41" t="n">
-        <v>16.05939702887148</v>
+        <v>2.609652017191616</v>
       </c>
       <c r="E41" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F41" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>19.93798305817884</v>
+        <v>3.239922246954062</v>
       </c>
       <c r="D42" t="n">
-        <v>17.45872068605397</v>
+        <v>2.837042111483771</v>
       </c>
       <c r="E42" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F42" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>25.79602782912802</v>
+        <v>4.191854522233304</v>
       </c>
       <c r="D43" t="n">
-        <v>15.40292180074936</v>
+        <v>2.502974792621771</v>
       </c>
       <c r="E43" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F43" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>29.08163055139305</v>
+        <v>4.725764964601371</v>
       </c>
       <c r="D44" t="n">
-        <v>26.98883984535473</v>
+        <v>4.385686474870144</v>
       </c>
       <c r="E44" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F44" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>30.38844565695416</v>
+        <v>4.938122419255051</v>
       </c>
       <c r="D45" t="n">
-        <v>27.75623730266196</v>
+        <v>4.510388561682569</v>
       </c>
       <c r="E45" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F45" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>37.06589728205683</v>
+        <v>6.023208308334235</v>
       </c>
       <c r="D46" t="n">
-        <v>17.24093964956667</v>
+        <v>2.801652693054583</v>
       </c>
       <c r="E46" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F46" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>36.74329140988146</v>
+        <v>5.970784854105737</v>
       </c>
       <c r="D47" t="n">
-        <v>32.51538097577821</v>
+        <v>5.28374940856396</v>
       </c>
       <c r="E47" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F47" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>16.52237689044586</v>
+        <v>2.684886244697452</v>
       </c>
       <c r="D48" t="n">
-        <v>16.31334901084091</v>
+        <v>2.650919214261647</v>
       </c>
       <c r="E48" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F48" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>41.06390801357803</v>
+        <v>6.67288505220643</v>
       </c>
       <c r="D49" t="n">
-        <v>24.74873734152916</v>
+        <v>4.02166981799849</v>
       </c>
       <c r="E49" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F49" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>40.00053666290043</v>
+        <v>6.50008720772132</v>
       </c>
       <c r="D50" t="n">
-        <v>9.013878188659973</v>
+        <v>1.464755205657246</v>
       </c>
       <c r="E50" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F50" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>52.02661201633433</v>
+        <v>8.454324452654328</v>
       </c>
       <c r="D51" t="n">
-        <v>32.31098884280702</v>
+        <v>5.250535686956141</v>
       </c>
       <c r="E51" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F51" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>85.066991660407</v>
+        <v>13.82338614481614</v>
       </c>
       <c r="D52" t="n">
-        <v>19.9501113892741</v>
+        <v>3.241893100757042</v>
       </c>
       <c r="E52" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F52" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>50.78193557019087</v>
+        <v>8.252064530156016</v>
       </c>
       <c r="D53" t="n">
-        <v>20.52551261941858</v>
+        <v>3.335395800655519</v>
       </c>
       <c r="E53" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F53" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>72.24167093968451</v>
+        <v>11.73927152769873</v>
       </c>
       <c r="D54" t="n">
-        <v>18.97366596101028</v>
+        <v>3.08322071866417</v>
       </c>
       <c r="E54" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F54" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>26.73684220175159</v>
+        <v>4.344736857784634</v>
       </c>
       <c r="D55" t="n">
-        <v>26.61164949492219</v>
+        <v>4.324393042924855</v>
       </c>
       <c r="E55" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F55" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>22.96312425078331</v>
+        <v>3.731507690752288</v>
       </c>
       <c r="D56" t="n">
-        <v>8.822642011852372</v>
+        <v>1.43367932692601</v>
       </c>
       <c r="E56" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F56" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>38.07296585779371</v>
+        <v>6.186856951891478</v>
       </c>
       <c r="D57" t="n">
-        <v>30.11138172678809</v>
+        <v>4.893099530603065</v>
       </c>
       <c r="E57" t="n">
-        <v>20.68272687959177</v>
+        <v>3.360943117933662</v>
       </c>
       <c r="F57" t="n">
-        <v>12.52197961471767</v>
+        <v>2.034821687391621</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
